--- a/Excel/SAP.XLSX
+++ b/Excel/SAP.XLSX
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24701"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DANIEL\ANTIGRAVITY\PROJEK\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01682403-FBAD-422A-9059-3FDAF47C95CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21855" windowHeight="14940"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -31,9 +40,6 @@
     <t>PC</t>
   </si>
   <si>
-    <t>COMP 2 KUNCI B DOOR LOCK D5 L PR</t>
-  </si>
-  <si>
     <t>M3</t>
   </si>
   <si>
@@ -488,29 +494,39 @@
   </si>
   <si>
     <t>Indicator: Multiple Specifications</t>
+  </si>
+  <si>
+    <t>Ini testing Tab pada Material</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="169" formatCode="#,##0.000"/>
-    <numFmt numFmtId="170" formatCode="#,##0.0"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
-      <u/>
-      <sz val="10"/>
-      <color indexed="12"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -525,13 +541,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="13"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="43"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -562,12 +572,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -580,539 +587,829 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 15" xfId="1" xr:uid="{AE7306FA-7279-496F-95F2-842290884C9D}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DV2"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" bestFit="1" width="10" customWidth="1"/>
-    <col min="2" max="2" bestFit="1" width="10" customWidth="1"/>
-    <col min="3" max="3" bestFit="1" width="21" customWidth="1"/>
-    <col min="4" max="4" bestFit="1" width="15" customWidth="1"/>
-    <col min="5" max="5" bestFit="1" width="16" customWidth="1"/>
-    <col min="6" max="6" bestFit="1" width="13" customWidth="1"/>
-    <col min="7" max="7" bestFit="1" width="34" customWidth="1"/>
-    <col min="8" max="8" bestFit="1" width="10" customWidth="1"/>
-    <col min="9" max="9" bestFit="1" width="15" customWidth="1"/>
-    <col min="10" max="10" bestFit="1" width="18" customWidth="1"/>
-    <col min="11" max="11" bestFit="1" width="10" customWidth="1"/>
-    <col min="12" max="12" bestFit="1" width="9" customWidth="1"/>
-    <col min="13" max="13" bestFit="1" width="11" customWidth="1"/>
-    <col min="14" max="14" bestFit="1" width="7" customWidth="1"/>
-    <col min="15" max="15" bestFit="1" width="18" customWidth="1"/>
-    <col min="16" max="16" bestFit="1" width="20" customWidth="1"/>
-    <col min="17" max="17" bestFit="1" width="22" customWidth="1"/>
-    <col min="18" max="18" bestFit="1" width="16" customWidth="1"/>
-    <col min="19" max="19" bestFit="1" width="12" customWidth="1"/>
-    <col min="20" max="20" bestFit="1" width="13" customWidth="1"/>
-    <col min="21" max="21" bestFit="1" width="11" customWidth="1"/>
-    <col min="22" max="22" bestFit="1" width="9" customWidth="1"/>
-    <col min="23" max="23" bestFit="1" width="6" customWidth="1"/>
-    <col min="24" max="24" bestFit="1" width="21" customWidth="1"/>
-    <col min="25" max="25" bestFit="1" width="13" customWidth="1"/>
-    <col min="26" max="26" bestFit="1" width="13" customWidth="1"/>
-    <col min="27" max="27" bestFit="1" width="13" customWidth="1"/>
-    <col min="28" max="28" bestFit="1" width="13" customWidth="1"/>
-    <col min="29" max="29" bestFit="1" width="13" customWidth="1"/>
-    <col min="30" max="30" bestFit="1" width="13" customWidth="1"/>
-    <col min="31" max="31" bestFit="1" width="15" customWidth="1"/>
-    <col min="32" max="32" bestFit="1" width="6" customWidth="1"/>
-    <col min="33" max="33" bestFit="1" width="15" customWidth="1"/>
-    <col min="34" max="34" bestFit="1" width="11" customWidth="1"/>
-    <col min="35" max="35" bestFit="1" width="15" customWidth="1"/>
-    <col min="36" max="36" bestFit="1" width="6" customWidth="1"/>
-    <col min="37" max="37" bestFit="1" width="13" customWidth="1"/>
-    <col min="38" max="38" bestFit="1" width="11" customWidth="1"/>
-    <col min="39" max="39" bestFit="1" width="11" customWidth="1"/>
-    <col min="40" max="40" bestFit="1" width="9" customWidth="1"/>
-    <col min="41" max="41" bestFit="1" width="14" customWidth="1"/>
-    <col min="42" max="42" bestFit="1" width="8" customWidth="1"/>
-    <col min="43" max="43" bestFit="1" width="17" customWidth="1"/>
-    <col min="44" max="44" bestFit="1" width="11" customWidth="1"/>
-    <col min="45" max="45" bestFit="1" width="8" customWidth="1"/>
-    <col min="46" max="46" bestFit="1" width="7" customWidth="1"/>
-    <col min="47" max="47" bestFit="1" width="8" customWidth="1"/>
-    <col min="48" max="48" bestFit="1" width="19" customWidth="1"/>
-    <col min="49" max="49" bestFit="1" width="9" customWidth="1"/>
-    <col min="50" max="50" bestFit="1" width="13" customWidth="1"/>
-    <col min="51" max="51" bestFit="1" width="12" customWidth="1"/>
-    <col min="52" max="52" bestFit="1" width="8" customWidth="1"/>
-    <col min="53" max="53" bestFit="1" width="18" customWidth="1"/>
-    <col min="54" max="54" bestFit="1" width="13" customWidth="1"/>
-    <col min="55" max="55" bestFit="1" width="17" customWidth="1"/>
-    <col min="56" max="56" bestFit="1" width="7" customWidth="1"/>
-    <col min="57" max="57" bestFit="1" width="7" customWidth="1"/>
-    <col min="58" max="58" bestFit="1" width="16" customWidth="1"/>
-    <col min="59" max="59" bestFit="1" width="10" customWidth="1"/>
-    <col min="60" max="60" bestFit="1" width="11" customWidth="1"/>
-    <col min="61" max="61" bestFit="1" width="5" customWidth="1"/>
-    <col min="62" max="62" bestFit="1" width="10" customWidth="1"/>
-    <col min="63" max="63" bestFit="1" width="14" customWidth="1"/>
-    <col min="64" max="64" bestFit="1" width="14" customWidth="1"/>
-    <col min="65" max="65" bestFit="1" width="16" customWidth="1"/>
-    <col min="66" max="66" bestFit="1" width="11" customWidth="1"/>
-    <col min="67" max="67" bestFit="1" width="26" customWidth="1"/>
-    <col min="68" max="68" bestFit="1" width="12" customWidth="1"/>
-    <col min="69" max="69" bestFit="1" width="12" customWidth="1"/>
-    <col min="70" max="70" bestFit="1" width="15" customWidth="1"/>
-    <col min="71" max="71" bestFit="1" width="12" customWidth="1"/>
-    <col min="72" max="72" bestFit="1" width="14" customWidth="1"/>
-    <col min="73" max="73" bestFit="1" width="14" customWidth="1"/>
-    <col min="74" max="74" bestFit="1" width="10" customWidth="1"/>
-    <col min="75" max="75" bestFit="1" width="18" customWidth="1"/>
-    <col min="76" max="76" bestFit="1" width="16" customWidth="1"/>
-    <col min="77" max="77" bestFit="1" width="16" customWidth="1"/>
-    <col min="78" max="78" bestFit="1" width="11" customWidth="1"/>
-    <col min="79" max="79" bestFit="1" width="13" customWidth="1"/>
-    <col min="80" max="80" bestFit="1" width="12" customWidth="1"/>
-    <col min="81" max="81" bestFit="1" width="18" customWidth="1"/>
-    <col min="82" max="82" bestFit="1" width="13" customWidth="1"/>
-    <col min="83" max="83" bestFit="1" width="15" customWidth="1"/>
-    <col min="84" max="84" bestFit="1" width="18" customWidth="1"/>
-    <col min="85" max="85" bestFit="1" width="21" customWidth="1"/>
-    <col min="86" max="86" bestFit="1" width="8" customWidth="1"/>
-    <col min="87" max="87" bestFit="1" width="16" customWidth="1"/>
-    <col min="88" max="88" bestFit="1" width="15" customWidth="1"/>
-    <col min="89" max="89" bestFit="1" width="16" customWidth="1"/>
-    <col min="90" max="90" bestFit="1" width="14" customWidth="1"/>
-    <col min="91" max="91" bestFit="1" width="11" customWidth="1"/>
-    <col min="92" max="92" bestFit="1" width="18" customWidth="1"/>
-    <col min="93" max="93" bestFit="1" width="13" customWidth="1"/>
-    <col min="94" max="94" bestFit="1" width="32" customWidth="1"/>
-    <col min="95" max="95" bestFit="1" width="17" customWidth="1"/>
-    <col min="96" max="96" bestFit="1" width="11" customWidth="1"/>
-    <col min="97" max="97" bestFit="1" width="15" customWidth="1"/>
-    <col min="98" max="98" bestFit="1" width="37" customWidth="1"/>
-    <col min="99" max="99" bestFit="1" width="42" customWidth="1"/>
-    <col min="100" max="100" bestFit="1" width="42" customWidth="1"/>
-    <col min="101" max="101" bestFit="1" width="20" customWidth="1"/>
-    <col min="102" max="102" bestFit="1" width="16" customWidth="1"/>
-    <col min="103" max="103" bestFit="1" width="15" customWidth="1"/>
-    <col min="104" max="104" bestFit="1" width="19" customWidth="1"/>
-    <col min="105" max="105" bestFit="1" width="19" customWidth="1"/>
-    <col min="106" max="106" bestFit="1" width="27" customWidth="1"/>
-    <col min="107" max="107" bestFit="1" width="13" customWidth="1"/>
-    <col min="108" max="108" bestFit="1" width="17" customWidth="1"/>
-    <col min="109" max="109" bestFit="1" width="15" customWidth="1"/>
-    <col min="110" max="110" bestFit="1" width="15" customWidth="1"/>
-    <col min="111" max="111" bestFit="1" width="37" customWidth="1"/>
-    <col min="112" max="112" bestFit="1" width="19" customWidth="1"/>
-    <col min="113" max="113" bestFit="1" width="16" customWidth="1"/>
-    <col min="114" max="114" bestFit="1" width="41" customWidth="1"/>
-    <col min="115" max="115" bestFit="1" width="23" customWidth="1"/>
-    <col min="116" max="116" bestFit="1" width="42" customWidth="1"/>
-    <col min="117" max="117" bestFit="1" width="41" customWidth="1"/>
-    <col min="118" max="118" bestFit="1" width="42" customWidth="1"/>
-    <col min="119" max="119" bestFit="1" width="23" customWidth="1"/>
-    <col min="120" max="120" bestFit="1" width="27" customWidth="1"/>
-    <col min="121" max="121" bestFit="1" width="41" customWidth="1"/>
-    <col min="122" max="122" bestFit="1" width="41" customWidth="1"/>
-    <col min="123" max="123" bestFit="1" width="34" customWidth="1"/>
-    <col min="124" max="124" bestFit="1" width="35" customWidth="1"/>
-    <col min="125" max="125" bestFit="1" width="30" customWidth="1"/>
-    <col min="126" max="126" bestFit="1" width="36" customWidth="1"/>
+    <col min="1" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="21" bestFit="1" customWidth="1"/>
+    <col min="25" max="30" width="13" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="15" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="6" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="15" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="15" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="6" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="11" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="9" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="8" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="17" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="11" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="8" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="7" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="8" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="19" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="9" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="13" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="12" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="8" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="18" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="13" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="17" bestFit="1" customWidth="1"/>
+    <col min="56" max="57" width="7" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="16" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="10" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="11" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="5" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="10" bestFit="1" customWidth="1"/>
+    <col min="63" max="64" width="14" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="16" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="11" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="26" bestFit="1" customWidth="1"/>
+    <col min="68" max="69" width="12" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="15" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="12" bestFit="1" customWidth="1"/>
+    <col min="72" max="73" width="14" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="10" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="18" bestFit="1" customWidth="1"/>
+    <col min="76" max="77" width="16" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="11" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="13" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="12" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="18" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="13" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="15" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="18" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="21" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="8" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="16" bestFit="1" customWidth="1"/>
+    <col min="88" max="88" width="15" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="16" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="14" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="11" bestFit="1" customWidth="1"/>
+    <col min="92" max="92" width="18" bestFit="1" customWidth="1"/>
+    <col min="93" max="93" width="13" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="32" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="17" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="11" bestFit="1" customWidth="1"/>
+    <col min="97" max="97" width="15" bestFit="1" customWidth="1"/>
+    <col min="98" max="98" width="37" bestFit="1" customWidth="1"/>
+    <col min="99" max="100" width="42" bestFit="1" customWidth="1"/>
+    <col min="101" max="101" width="20" bestFit="1" customWidth="1"/>
+    <col min="102" max="102" width="16" bestFit="1" customWidth="1"/>
+    <col min="103" max="103" width="15" bestFit="1" customWidth="1"/>
+    <col min="104" max="105" width="19" bestFit="1" customWidth="1"/>
+    <col min="106" max="106" width="27" bestFit="1" customWidth="1"/>
+    <col min="107" max="107" width="13" bestFit="1" customWidth="1"/>
+    <col min="108" max="108" width="17" bestFit="1" customWidth="1"/>
+    <col min="109" max="110" width="15" bestFit="1" customWidth="1"/>
+    <col min="111" max="111" width="37" bestFit="1" customWidth="1"/>
+    <col min="112" max="112" width="19" bestFit="1" customWidth="1"/>
+    <col min="113" max="113" width="16" bestFit="1" customWidth="1"/>
+    <col min="114" max="114" width="41" bestFit="1" customWidth="1"/>
+    <col min="115" max="115" width="23" bestFit="1" customWidth="1"/>
+    <col min="116" max="116" width="42" bestFit="1" customWidth="1"/>
+    <col min="117" max="117" width="41" bestFit="1" customWidth="1"/>
+    <col min="118" max="118" width="42" bestFit="1" customWidth="1"/>
+    <col min="119" max="119" width="23" bestFit="1" customWidth="1"/>
+    <col min="120" max="120" width="27" bestFit="1" customWidth="1"/>
+    <col min="121" max="122" width="41" bestFit="1" customWidth="1"/>
+    <col min="123" max="123" width="34" bestFit="1" customWidth="1"/>
+    <col min="124" max="124" width="35" bestFit="1" customWidth="1"/>
+    <col min="125" max="125" width="30" bestFit="1" customWidth="1"/>
+    <col min="126" max="126" width="36" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:126">
+    <row r="1" spans="1:126" ht="50" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="X1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AG1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="AH1" s="6" t="s">
+      <c r="AI1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AJ1" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="AJ1" s="6" t="s">
+      <c r="AK1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AN1" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="AN1" s="6" t="s">
+      <c r="AO1" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="AO1" s="6" t="s">
+      <c r="AP1" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="AP1" s="6" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AW1" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="AW1" s="6" t="s">
+      <c r="AX1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BE1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BF1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BG1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BH1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BI1" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="BI1" s="6" t="s">
+      <c r="BJ1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BK1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BL1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BM1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BN1" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="BN1" s="6" t="s">
+      <c r="BO1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BP1" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="BP1" s="6" t="s">
+      <c r="BQ1" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="BQ1" s="6" t="s">
+      <c r="BR1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BS1" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="BS1" s="6" t="s">
+      <c r="BT1" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="BT1" s="6" t="s">
+      <c r="BU1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BV1" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="BV1" s="6" t="s">
+      <c r="BW1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="BX1" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="BX1" s="6" t="s">
+      <c r="BY1" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="BY1" s="6" t="s">
+      <c r="BZ1" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="BZ1" s="6" t="s">
+      <c r="CA1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CB1" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="CB1" s="6" t="s">
+      <c r="CC1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CD1" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="CD1" s="6" t="s">
+      <c r="CE1" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CF1" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="CF1" s="6" t="s">
+      <c r="CG1" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="CG1" s="1" t="s">
+      <c r="CH1" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="CH1" s="6" t="s">
+      <c r="CI1" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="CI1" s="6" t="s">
+      <c r="CJ1" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="CJ1" s="6" t="s">
+      <c r="CK1" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="CK1" s="1" t="s">
+      <c r="CL1" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="CL1" s="6" t="s">
+      <c r="CM1" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="CM1" s="6" t="s">
+      <c r="CN1" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="CN1" s="1" t="s">
+      <c r="CO1" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="CO1" s="1" t="s">
+      <c r="CP1" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="CP1" s="1" t="s">
+      <c r="CQ1" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="CQ1" s="6" t="s">
+      <c r="CR1" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="CR1" s="6" t="s">
+      <c r="CS1" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="CS1" s="6" t="s">
+      <c r="CT1" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="CT1" s="1" t="s">
+      <c r="CU1" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="CU1" s="1" t="s">
+      <c r="CV1" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="CV1" s="1" t="s">
+      <c r="CW1" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="CW1" s="6" t="s">
+      <c r="CX1" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="CX1" s="6" t="s">
+      <c r="CY1" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="CY1" s="6" t="s">
+      <c r="CZ1" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="CZ1" s="6" t="s">
+      <c r="DA1" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="DB1" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="DA1" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="DB1" s="1" t="s">
+      <c r="DC1" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="DC1" s="6" t="s">
+      <c r="DD1" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="DD1" s="1" t="s">
+      <c r="DE1" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="DE1" s="6" t="s">
+      <c r="DF1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="DG1" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="DF1" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="DG1" s="1" t="s">
+      <c r="DH1" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="DH1" s="6" t="s">
+      <c r="DI1" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="DI1" s="6" t="s">
+      <c r="DJ1" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="DJ1" s="1" t="s">
+      <c r="DK1" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="DK1" s="6" t="s">
+      <c r="DL1" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="DL1" s="1" t="s">
+      <c r="DM1" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="DM1" s="1" t="s">
+      <c r="DN1" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="DN1" s="1" t="s">
+      <c r="DO1" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="DO1" s="6" t="s">
+      <c r="DP1" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="DP1" s="1" t="s">
+      <c r="DQ1" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="DQ1" s="1" t="s">
+      <c r="DR1" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="DR1" s="1" t="s">
+      <c r="DS1" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="DS1" s="1" t="s">
+      <c r="DT1" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="DT1" s="1" t="s">
+      <c r="DU1" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="DU1" s="1" t="s">
+      <c r="DV1" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="DV1" s="1" t="s">
-        <v>158</v>
-      </c>
     </row>
-    <row r="2" spans="1:126">
+    <row r="2" spans="1:126" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1131,333 +1428,333 @@
       <c r="F2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="H2" t="s">
         <v>6</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>7</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
+        <v>2</v>
+      </c>
+      <c r="K2" t="s">
         <v>8</v>
       </c>
-      <c r="J2" t="s">
-        <v>2</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M2" t="s">
         <v>9</v>
       </c>
-      <c r="L2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>10</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>2</v>
+      </c>
+      <c r="R2" t="s">
+        <v>2</v>
+      </c>
+      <c r="S2" t="s">
+        <v>2</v>
+      </c>
+      <c r="T2" t="s">
         <v>11</v>
       </c>
-      <c r="O2" t="s">
-        <v>2</v>
-      </c>
-      <c r="P2" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>2</v>
-      </c>
-      <c r="R2" t="s">
-        <v>2</v>
-      </c>
-      <c r="S2" t="s">
-        <v>2</v>
-      </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>12</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>13</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
+        <v>7</v>
+      </c>
+      <c r="X2" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD2" t="s">
         <v>14</v>
       </c>
-      <c r="W2" t="s">
-        <v>8</v>
-      </c>
-      <c r="X2" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD2" t="s">
+      <c r="AE2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF2" t="s">
         <v>15</v>
       </c>
-      <c r="AE2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF2" t="s">
+      <c r="AG2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AH2" t="s">
         <v>16</v>
       </c>
-      <c r="AG2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AH2" t="s">
+      <c r="AI2" t="s">
         <v>17</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AJ2" t="s">
         <v>18</v>
       </c>
-      <c r="AJ2" t="s">
-        <v>19</v>
-      </c>
       <c r="AK2" s="2">
-        <v>1.14</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="AL2" s="2">
-        <v>0.00</v>
+        <v>0</v>
       </c>
       <c r="AM2" s="3">
         <v>1</v>
       </c>
       <c r="AN2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AO2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AR2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AS2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AW2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="s">
         <v>20</v>
       </c>
-      <c r="AO2" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP2" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AR2" s="3">
-        <v>0</v>
-      </c>
-      <c r="AS2" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="AT2" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="AU2" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AW2" s="3">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="s">
+      <c r="AY2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AZ2" s="3">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BG2" t="s">
         <v>21</v>
       </c>
-      <c r="AY2" s="3">
-        <v>0</v>
-      </c>
-      <c r="AZ2" s="3">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BG2" t="s">
+      <c r="BH2" t="s">
         <v>22</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BI2" t="s">
         <v>23</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BJ2" t="s">
         <v>24</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BK2" s="4">
+        <v>0</v>
+      </c>
+      <c r="BL2" s="4">
+        <v>0</v>
+      </c>
+      <c r="BM2" s="4">
+        <v>0</v>
+      </c>
+      <c r="BN2" t="s">
         <v>25</v>
       </c>
-      <c r="BK2" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="BL2" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="BM2" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="BN2" t="s">
+      <c r="BO2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BP2" t="s">
+        <v>12</v>
+      </c>
+      <c r="BQ2" s="3">
+        <v>0</v>
+      </c>
+      <c r="BR2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BS2" s="3">
+        <v>0</v>
+      </c>
+      <c r="BT2" t="s">
         <v>26</v>
       </c>
-      <c r="BO2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BP2" t="s">
-        <v>13</v>
-      </c>
-      <c r="BQ2" s="3">
-        <v>0</v>
-      </c>
-      <c r="BR2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BS2" s="3">
-        <v>0</v>
-      </c>
-      <c r="BT2" t="s">
+      <c r="BU2" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV2" t="s">
         <v>27</v>
       </c>
-      <c r="BU2" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="BV2" t="s">
+      <c r="BW2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BX2" t="s">
+        <v>8</v>
+      </c>
+      <c r="BY2" t="s">
+        <v>8</v>
+      </c>
+      <c r="BZ2" t="s">
         <v>28</v>
       </c>
-      <c r="BW2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BX2" t="s">
-        <v>9</v>
-      </c>
-      <c r="BY2" t="s">
-        <v>9</v>
-      </c>
-      <c r="BZ2" t="s">
+      <c r="CA2" t="s">
+        <v>2</v>
+      </c>
+      <c r="CB2" t="s">
         <v>29</v>
       </c>
-      <c r="CA2" t="s">
-        <v>2</v>
-      </c>
-      <c r="CB2" t="s">
+      <c r="CC2" t="s">
+        <v>2</v>
+      </c>
+      <c r="CD2" t="s">
+        <v>12</v>
+      </c>
+      <c r="CE2" t="s">
+        <v>2</v>
+      </c>
+      <c r="CF2" t="s">
         <v>30</v>
       </c>
-      <c r="CC2" t="s">
-        <v>2</v>
-      </c>
-      <c r="CD2" t="s">
-        <v>13</v>
-      </c>
-      <c r="CE2" t="s">
-        <v>2</v>
-      </c>
-      <c r="CF2" t="s">
+      <c r="CG2" t="s">
+        <v>2</v>
+      </c>
+      <c r="CH2" t="s">
         <v>31</v>
       </c>
-      <c r="CG2" t="s">
-        <v>2</v>
-      </c>
-      <c r="CH2" t="s">
+      <c r="CI2" s="5">
+        <v>0</v>
+      </c>
+      <c r="CJ2" s="5">
+        <v>0</v>
+      </c>
+      <c r="CK2" t="s">
+        <v>2</v>
+      </c>
+      <c r="CL2" t="s">
+        <v>16</v>
+      </c>
+      <c r="CM2" t="s">
+        <v>16</v>
+      </c>
+      <c r="CN2" s="4">
+        <v>100</v>
+      </c>
+      <c r="CO2" t="s">
+        <v>2</v>
+      </c>
+      <c r="CP2" t="s">
+        <v>2</v>
+      </c>
+      <c r="CQ2" t="s">
+        <v>14</v>
+      </c>
+      <c r="CR2" t="s">
         <v>32</v>
       </c>
-      <c r="CI2" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="CJ2" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="CK2" t="s">
-        <v>2</v>
-      </c>
-      <c r="CL2" t="s">
-        <v>17</v>
-      </c>
-      <c r="CM2" t="s">
-        <v>17</v>
-      </c>
-      <c r="CN2" s="4">
-        <v>100.000</v>
-      </c>
-      <c r="CO2" t="s">
-        <v>2</v>
-      </c>
-      <c r="CP2" t="s">
-        <v>2</v>
-      </c>
-      <c r="CQ2" t="s">
-        <v>15</v>
-      </c>
-      <c r="CR2" t="s">
+      <c r="CS2" t="s">
+        <v>16</v>
+      </c>
+      <c r="CT2" t="s">
+        <v>2</v>
+      </c>
+      <c r="CU2" t="s">
+        <v>2</v>
+      </c>
+      <c r="CV2" t="s">
+        <v>2</v>
+      </c>
+      <c r="CW2" t="s">
+        <v>16</v>
+      </c>
+      <c r="CX2" t="s">
+        <v>16</v>
+      </c>
+      <c r="CY2" t="s">
+        <v>16</v>
+      </c>
+      <c r="CZ2" t="s">
+        <v>16</v>
+      </c>
+      <c r="DA2" t="s">
+        <v>16</v>
+      </c>
+      <c r="DB2" t="s">
+        <v>2</v>
+      </c>
+      <c r="DC2" s="3">
+        <v>0</v>
+      </c>
+      <c r="DD2" t="s">
+        <v>2</v>
+      </c>
+      <c r="DE2" t="s">
+        <v>16</v>
+      </c>
+      <c r="DF2" t="s">
+        <v>16</v>
+      </c>
+      <c r="DG2" t="s">
+        <v>2</v>
+      </c>
+      <c r="DH2" t="s">
+        <v>16</v>
+      </c>
+      <c r="DI2" s="3">
+        <v>0</v>
+      </c>
+      <c r="DJ2" t="s">
+        <v>2</v>
+      </c>
+      <c r="DK2" t="s">
         <v>33</v>
       </c>
-      <c r="CS2" t="s">
-        <v>17</v>
-      </c>
-      <c r="CT2" t="s">
-        <v>2</v>
-      </c>
-      <c r="CU2" t="s">
-        <v>2</v>
-      </c>
-      <c r="CV2" t="s">
-        <v>2</v>
-      </c>
-      <c r="CW2" t="s">
-        <v>17</v>
-      </c>
-      <c r="CX2" t="s">
-        <v>17</v>
-      </c>
-      <c r="CY2" t="s">
-        <v>17</v>
-      </c>
-      <c r="CZ2" t="s">
-        <v>17</v>
-      </c>
-      <c r="DA2" t="s">
-        <v>17</v>
-      </c>
-      <c r="DB2" t="s">
-        <v>2</v>
-      </c>
-      <c r="DC2" s="3">
-        <v>0</v>
-      </c>
-      <c r="DD2" t="s">
-        <v>2</v>
-      </c>
-      <c r="DE2" t="s">
-        <v>17</v>
-      </c>
-      <c r="DF2" t="s">
-        <v>17</v>
-      </c>
-      <c r="DG2" t="s">
-        <v>2</v>
-      </c>
-      <c r="DH2" t="s">
-        <v>17</v>
-      </c>
-      <c r="DI2" s="3">
-        <v>0</v>
-      </c>
-      <c r="DJ2" t="s">
-        <v>2</v>
-      </c>
-      <c r="DK2" t="s">
-        <v>34</v>
-      </c>
       <c r="DL2" t="s">
         <v>2</v>
       </c>
@@ -1468,7 +1765,7 @@
         <v>2</v>
       </c>
       <c r="DO2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="DP2" t="s">
         <v>2</v>
